--- a/output/2026-09-05_16_Italia_Sicilia_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-05_16_Italia_Sicilia_Utensilerie_e_Macchine_Utensili.xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -573,7 +573,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,6 @@
           <t>Utensili elettrici, strumenti di misura, saldatrici, abrasivi, utensili da taglio, accessori macchine utensili, pneumatica</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Storica dal 1962, clientela professionale (serramentisti, fabbri) e privati/DIY. Fit B2B moderato (generalista con forte componente professionale). Telefono non reperito.</t>
@@ -791,7 +790,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -828,7 +827,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -865,7 +864,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -902,7 +901,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -939,7 +938,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -976,7 +975,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
